--- a/artfynd/A 29324-2023 artfynd.xlsx
+++ b/artfynd/A 29324-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29324-2023 artfynd.xlsx
+++ b/artfynd/A 29324-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110396684</v>
+        <v>110396685</v>
       </c>
       <c r="B4" t="n">
         <v>96367</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512607.8942393544</v>
+        <v>512533.3968774515</v>
       </c>
       <c r="R4" t="n">
-        <v>6951491.416693274</v>
+        <v>6951373.592836751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110396685</v>
+        <v>110396687</v>
       </c>
       <c r="B5" t="n">
         <v>96367</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512533.3968774515</v>
+        <v>512531.6745066461</v>
       </c>
       <c r="R5" t="n">
-        <v>6951373.592836751</v>
+        <v>6951342.823159757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,123 +1140,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>110396687</v>
-      </c>
-      <c r="B6" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Mjölksjöån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>512531.6745066461</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6951342.823159757</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
